--- a/templates/form_template.xlsx
+++ b/templates/form_template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ndous\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{AB401471-A610-4401-B85B-0F9A47F8C839}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3353A869-9F86-46A6-9E5A-BD52B0C68D29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -222,106 +222,67 @@
   </si>
   <si>
     <t>Expense Info</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>Tax code</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>/GST code</t>
-    </r>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>Sales contract number</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">KRW </t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>KR-Domestic Business Travel - Accommodation</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>KR-Domestic Business Travel - Parking and Toll Charges</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>KR-Overseas Business Travel - Airfare</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>KR-Domestic Business Travel - Car Rental/Fuel Costs</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>KR-TELEPHONE EXPENSES</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>KR-Overseas Business Travel - Accommodation</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>KR-Overseas Business Travel - Other Transportation</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>KR-Business Entertainment Expenses</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Tax code/GST code</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="11">
+  <numFmts count="1">
+    <numFmt numFmtId="176" formatCode="#,##0_);[Red]\(#,##0\)"/>
+  </numFmts>
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color indexed="8"/>
       <name val="맑은 고딕"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="맑은 고딕"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color indexed="8"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color indexed="8"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color indexed="55"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
@@ -340,17 +301,19 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
+      <color indexed="8"/>
+      <name val="맑은 고딕"/>
       <family val="3"/>
-      <charset val="134"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF000000"/>
+      <color indexed="8"/>
       <name val="맑은 고딕"/>
       <family val="3"/>
       <charset val="129"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <b/>
@@ -359,15 +322,41 @@
       <name val="맑은 고딕"/>
       <family val="3"/>
       <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color indexed="55"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <sz val="10"/>
-      <name val="굴림"/>
+      <name val="맑은 고딕"/>
       <family val="3"/>
       <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -392,18 +381,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF92D050"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor indexed="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -535,88 +512,109 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0">
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="5" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="8" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="1" applyFill="1">
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="176" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1">
+    <xf numFmtId="176" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="0" fillId="7" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="10" fillId="7" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="3" xfId="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -934,398 +932,414 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:Q15"/>
-  <sheetFormatPr defaultRowHeight="16.5"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="2" width="20" hidden="1" customWidth="1"/>
-    <col min="3" max="3" width="49.875" customWidth="1"/>
-    <col min="4" max="4" width="21.75" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="15.875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.625" hidden="1" customWidth="1"/>
-    <col min="7" max="7" width="13.75" hidden="1" customWidth="1"/>
-    <col min="8" max="9" width="20" customWidth="1"/>
-    <col min="10" max="14" width="20" hidden="1" customWidth="1"/>
-    <col min="15" max="15" width="23.125" style="12" customWidth="1"/>
-    <col min="16" max="17" width="20" hidden="1" customWidth="1"/>
+    <col min="1" max="2" width="20" style="4" hidden="1" customWidth="1"/>
+    <col min="3" max="3" width="49.875" style="4" customWidth="1"/>
+    <col min="4" max="4" width="21.75" style="4" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.875" style="4" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.625" style="4" hidden="1" customWidth="1"/>
+    <col min="7" max="7" width="13.75" style="4" hidden="1" customWidth="1"/>
+    <col min="8" max="8" width="20" style="31" customWidth="1"/>
+    <col min="9" max="9" width="20" style="4" customWidth="1"/>
+    <col min="10" max="14" width="20" style="4" hidden="1" customWidth="1"/>
+    <col min="15" max="15" width="23.125" style="32" customWidth="1"/>
+    <col min="16" max="17" width="20" style="4" hidden="1" customWidth="1"/>
+    <col min="18" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="100.9" customHeight="1">
-      <c r="A1" s="24" t="s">
+    <row r="1" spans="1:17" ht="100.9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="24" t="s">
+      <c r="B1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="24" t="s">
+      <c r="C1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="24" t="s">
+      <c r="D1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="E1" s="24"/>
-      <c r="F1" s="24" t="s">
+      <c r="E1" s="3"/>
+      <c r="F1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="G1" s="24" t="s">
+      <c r="G1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="H1" s="24" t="s">
+      <c r="H1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="I1" s="24" t="s">
+      <c r="I1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="J1" s="24" t="s">
+      <c r="J1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="K1" s="24" t="s">
+      <c r="K1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="L1" s="24" t="s">
+      <c r="L1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="M1" s="24" t="s">
+      <c r="M1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="N1" s="24" t="s">
+      <c r="N1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="O1" s="24" t="s">
+      <c r="O1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="P1" s="24" t="s">
+      <c r="P1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="Q1" s="24" t="s">
+      <c r="Q1" s="3" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:17" ht="16.899999999999999" customHeight="1">
-      <c r="A2" s="24" t="s">
+    <row r="2" spans="1:17" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="24" t="s">
+      <c r="B2" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="24" t="s">
+      <c r="C2" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D2" s="24" t="s">
+      <c r="D2" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="E2" s="24"/>
-      <c r="F2" s="24" t="s">
+      <c r="E2" s="3"/>
+      <c r="F2" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="G2" s="24" t="s">
+      <c r="G2" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="H2" s="24" t="s">
+      <c r="H2" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="I2" s="24" t="s">
+      <c r="I2" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="J2" s="24" t="s">
+      <c r="J2" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="K2" s="24" t="s">
+      <c r="K2" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="L2" s="24" t="s">
+      <c r="L2" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="M2" s="24" t="s">
+      <c r="M2" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="N2" s="24" t="s">
+      <c r="N2" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="O2" s="24" t="s">
+      <c r="O2" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="P2" s="24" t="s">
+      <c r="P2" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="Q2" s="24" t="s">
+      <c r="Q2" s="3" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:17" ht="22.15" customHeight="1">
-      <c r="A3" s="25" t="s">
+    <row r="3" spans="1:17" ht="22.15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="B3" s="25" t="s">
+      <c r="B3" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="25" t="s">
+      <c r="C3" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="25" t="s">
+      <c r="D3" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="E3" s="25"/>
-      <c r="F3" s="25" t="s">
+      <c r="E3" s="5"/>
+      <c r="F3" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="G3" s="25" t="s">
+      <c r="G3" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="H3" s="25" t="s">
+      <c r="H3" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="I3" s="25" t="s">
+      <c r="I3" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="J3" s="25" t="s">
+      <c r="J3" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="K3" s="25" t="s">
+      <c r="K3" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="L3" s="25" t="s">
+      <c r="L3" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="M3" s="25" t="s">
+      <c r="M3" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="N3" s="25" t="s">
+      <c r="N3" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="O3" s="25" t="s">
+      <c r="O3" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="P3" s="25" t="s">
+      <c r="P3" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="Q3" s="25" t="s">
+      <c r="Q3" s="5" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:17" s="6" customFormat="1" ht="39.4" customHeight="1">
-      <c r="A4" s="5" t="s">
+    <row r="4" spans="1:17" s="9" customFormat="1" ht="39.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="5" t="s">
+      <c r="B4" s="6" t="s">
         <v>54</v>
       </c>
       <c r="C4" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="D4" s="5" t="s">
+      <c r="D4" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="E4" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="F4" s="5" t="s">
+      <c r="E4" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="F4" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="G4" s="5" t="s">
+      <c r="G4" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="H4" s="5" t="s">
+      <c r="H4" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="I4" s="5" t="s">
+      <c r="I4" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="J4" s="5" t="s">
+      <c r="J4" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="K4" s="5" t="s">
+      <c r="K4" s="6" t="s">
         <v>9</v>
       </c>
       <c r="L4" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="M4" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="N4" s="5" t="s">
+      <c r="M4" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="N4" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="O4" s="5" t="s">
+      <c r="O4" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="P4" s="5" t="s">
+      <c r="P4" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="Q4" s="5" t="s">
+      <c r="Q4" s="6" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="5" spans="1:17">
-      <c r="A5" s="9"/>
-      <c r="B5" s="10"/>
-      <c r="C5" s="23" t="s">
-        <v>70</v>
-      </c>
-      <c r="D5" s="16"/>
-      <c r="E5" s="1"/>
-      <c r="F5" s="13"/>
-      <c r="G5" s="1"/>
-      <c r="H5" s="20"/>
-      <c r="I5" s="21" t="s">
-        <v>62</v>
-      </c>
-      <c r="J5" s="2"/>
-      <c r="K5" s="2"/>
-      <c r="L5" s="1"/>
-      <c r="M5" s="1"/>
-      <c r="N5" s="1"/>
-      <c r="O5" s="8"/>
-      <c r="P5" s="10"/>
-      <c r="Q5" s="10"/>
-    </row>
-    <row r="6" spans="1:17">
-      <c r="C6" s="23" t="s">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A5" s="10"/>
+      <c r="B5" s="11"/>
+      <c r="C5" s="12" t="s">
+        <v>69</v>
+      </c>
+      <c r="D5" s="13"/>
+      <c r="E5" s="14"/>
+      <c r="F5" s="15"/>
+      <c r="G5" s="14"/>
+      <c r="H5" s="16"/>
+      <c r="I5" s="17" t="s">
+        <v>61</v>
+      </c>
+      <c r="J5" s="18"/>
+      <c r="K5" s="18"/>
+      <c r="L5" s="19"/>
+      <c r="M5" s="19"/>
+      <c r="N5" s="19"/>
+      <c r="O5" s="20"/>
+      <c r="P5" s="11"/>
+      <c r="Q5" s="11"/>
+    </row>
+    <row r="6" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="C6" s="12" t="s">
         <v>44</v>
       </c>
-      <c r="D6" s="16"/>
-      <c r="E6" s="1"/>
-      <c r="F6" s="9"/>
-      <c r="G6" s="9"/>
-      <c r="H6" s="20"/>
-      <c r="I6" s="21" t="s">
-        <v>62</v>
-      </c>
-      <c r="J6" s="2"/>
-      <c r="K6" s="2"/>
-      <c r="L6" s="1"/>
-      <c r="M6" s="1"/>
-      <c r="N6" s="1"/>
-      <c r="O6" s="8"/>
-    </row>
-    <row r="7" spans="1:17">
-      <c r="A7" s="11"/>
-      <c r="B7" s="15"/>
-      <c r="C7" s="23" t="s">
+      <c r="D6" s="13"/>
+      <c r="E6" s="14"/>
+      <c r="F6" s="21"/>
+      <c r="G6" s="21"/>
+      <c r="H6" s="16"/>
+      <c r="I6" s="17" t="s">
+        <v>61</v>
+      </c>
+      <c r="J6" s="18"/>
+      <c r="K6" s="18"/>
+      <c r="L6" s="19"/>
+      <c r="M6" s="19"/>
+      <c r="N6" s="19"/>
+      <c r="O6" s="20"/>
+    </row>
+    <row r="7" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A7" s="22"/>
+      <c r="B7" s="23"/>
+      <c r="C7" s="12" t="s">
         <v>44</v>
       </c>
-      <c r="D7" s="17"/>
-      <c r="E7" s="11"/>
-      <c r="H7" s="20"/>
-      <c r="I7" s="21" t="s">
-        <v>62</v>
-      </c>
-      <c r="J7" s="11"/>
-      <c r="K7" s="11"/>
-      <c r="L7" s="11"/>
-      <c r="M7" s="11"/>
-      <c r="N7" s="11"/>
-      <c r="O7" s="14"/>
-    </row>
-    <row r="8" spans="1:17">
-      <c r="A8" s="11"/>
-      <c r="B8" s="15"/>
-      <c r="C8" s="23" t="s">
+      <c r="D7" s="24"/>
+      <c r="E7" s="25"/>
+      <c r="F7" s="26"/>
+      <c r="G7" s="26"/>
+      <c r="H7" s="16"/>
+      <c r="I7" s="17" t="s">
+        <v>61</v>
+      </c>
+      <c r="J7" s="22"/>
+      <c r="K7" s="22"/>
+      <c r="L7" s="22"/>
+      <c r="M7" s="22"/>
+      <c r="N7" s="22"/>
+      <c r="O7" s="27"/>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A8" s="22"/>
+      <c r="B8" s="23"/>
+      <c r="C8" s="12" t="s">
         <v>44</v>
       </c>
-      <c r="D8" s="17"/>
-      <c r="E8" s="11"/>
-      <c r="H8" s="20"/>
-      <c r="I8" s="22" t="s">
-        <v>62</v>
-      </c>
-      <c r="J8" s="11"/>
-      <c r="K8" s="11"/>
-      <c r="L8" s="11"/>
-      <c r="M8" s="11"/>
-      <c r="N8" s="11"/>
-      <c r="O8" s="14"/>
-    </row>
-    <row r="9" spans="1:17">
-      <c r="C9" s="23" t="s">
+      <c r="D8" s="24"/>
+      <c r="E8" s="25"/>
+      <c r="F8" s="26"/>
+      <c r="G8" s="26"/>
+      <c r="H8" s="16"/>
+      <c r="I8" s="28" t="s">
+        <v>61</v>
+      </c>
+      <c r="J8" s="22"/>
+      <c r="K8" s="22"/>
+      <c r="L8" s="22"/>
+      <c r="M8" s="22"/>
+      <c r="N8" s="22"/>
+      <c r="O8" s="27"/>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="C9" s="12" t="s">
         <v>44</v>
       </c>
-      <c r="D9" s="17"/>
-      <c r="E9" s="11"/>
-      <c r="H9" s="20"/>
-      <c r="I9" s="21" t="s">
-        <v>62</v>
-      </c>
-      <c r="O9" s="14"/>
-    </row>
-    <row r="10" spans="1:17">
-      <c r="C10" s="23" t="s">
-        <v>67</v>
-      </c>
-      <c r="D10" s="17"/>
-      <c r="E10" s="11"/>
-      <c r="H10" s="19"/>
-      <c r="I10" s="21" t="s">
-        <v>62</v>
-      </c>
-      <c r="O10" s="14"/>
-    </row>
-    <row r="11" spans="1:17">
-      <c r="C11" s="23"/>
-      <c r="D11" s="17"/>
-      <c r="E11" s="11"/>
-      <c r="F11" s="11"/>
-      <c r="G11" s="11"/>
-      <c r="H11" s="20"/>
-      <c r="I11" s="21" t="s">
-        <v>62</v>
-      </c>
-      <c r="J11" s="11"/>
-      <c r="K11" s="11"/>
-      <c r="L11" s="11"/>
-      <c r="M11" s="11"/>
-      <c r="N11" s="11"/>
-      <c r="O11" s="14"/>
-    </row>
-    <row r="12" spans="1:17">
-      <c r="C12" s="23"/>
-      <c r="D12" s="18"/>
-      <c r="E12" s="18"/>
-      <c r="H12" s="20"/>
-      <c r="I12" s="21" t="s">
-        <v>62</v>
-      </c>
-      <c r="J12" s="11"/>
-      <c r="K12" s="11"/>
-      <c r="L12" s="11"/>
-      <c r="M12" s="11"/>
-      <c r="N12" s="11"/>
-      <c r="O12" s="14"/>
-    </row>
-    <row r="13" spans="1:17">
-      <c r="C13" s="23"/>
-      <c r="D13" s="11"/>
-      <c r="E13" s="11"/>
-      <c r="H13" s="20"/>
-      <c r="I13" s="21" t="s">
-        <v>62</v>
-      </c>
-      <c r="O13" s="14"/>
-    </row>
-    <row r="14" spans="1:17">
-      <c r="C14" s="23"/>
-      <c r="D14" s="11"/>
-      <c r="E14" s="11"/>
-      <c r="H14" s="20"/>
-      <c r="I14" s="21" t="s">
-        <v>62</v>
-      </c>
-      <c r="O14" s="14"/>
-    </row>
-    <row r="15" spans="1:17">
-      <c r="C15" s="23"/>
-      <c r="D15" s="11"/>
-      <c r="E15" s="11"/>
-      <c r="F15" s="11"/>
-      <c r="G15" s="11"/>
-      <c r="H15" s="19"/>
-      <c r="I15" s="21" t="s">
-        <v>62</v>
-      </c>
-      <c r="J15" s="11"/>
-      <c r="K15" s="11"/>
-      <c r="L15" s="11"/>
-      <c r="M15" s="11"/>
-      <c r="N15" s="11"/>
-      <c r="O15" s="14"/>
+      <c r="D9" s="24"/>
+      <c r="E9" s="25"/>
+      <c r="F9" s="26"/>
+      <c r="G9" s="26"/>
+      <c r="H9" s="16"/>
+      <c r="I9" s="17" t="s">
+        <v>61</v>
+      </c>
+      <c r="O9" s="27"/>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="C10" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="D10" s="24"/>
+      <c r="E10" s="25"/>
+      <c r="F10" s="26"/>
+      <c r="G10" s="26"/>
+      <c r="H10" s="29"/>
+      <c r="I10" s="17" t="s">
+        <v>61</v>
+      </c>
+      <c r="O10" s="27"/>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="C11" s="12"/>
+      <c r="D11" s="24"/>
+      <c r="E11" s="25"/>
+      <c r="F11" s="25"/>
+      <c r="G11" s="25"/>
+      <c r="H11" s="16"/>
+      <c r="I11" s="17" t="s">
+        <v>61</v>
+      </c>
+      <c r="J11" s="22"/>
+      <c r="K11" s="22"/>
+      <c r="L11" s="22"/>
+      <c r="M11" s="22"/>
+      <c r="N11" s="22"/>
+      <c r="O11" s="27"/>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="C12" s="12"/>
+      <c r="D12" s="30"/>
+      <c r="E12" s="30"/>
+      <c r="F12" s="26"/>
+      <c r="G12" s="26"/>
+      <c r="H12" s="16"/>
+      <c r="I12" s="17" t="s">
+        <v>61</v>
+      </c>
+      <c r="J12" s="22"/>
+      <c r="K12" s="22"/>
+      <c r="L12" s="22"/>
+      <c r="M12" s="22"/>
+      <c r="N12" s="22"/>
+      <c r="O12" s="27"/>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="C13" s="12"/>
+      <c r="D13" s="25"/>
+      <c r="E13" s="25"/>
+      <c r="F13" s="26"/>
+      <c r="G13" s="26"/>
+      <c r="H13" s="16"/>
+      <c r="I13" s="17" t="s">
+        <v>61</v>
+      </c>
+      <c r="O13" s="27"/>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="C14" s="12"/>
+      <c r="D14" s="25"/>
+      <c r="E14" s="25"/>
+      <c r="F14" s="26"/>
+      <c r="G14" s="26"/>
+      <c r="H14" s="16"/>
+      <c r="I14" s="17" t="s">
+        <v>61</v>
+      </c>
+      <c r="O14" s="27"/>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="C15" s="12"/>
+      <c r="D15" s="25"/>
+      <c r="E15" s="25"/>
+      <c r="F15" s="25"/>
+      <c r="G15" s="25"/>
+      <c r="H15" s="29"/>
+      <c r="I15" s="17" t="s">
+        <v>61</v>
+      </c>
+      <c r="J15" s="22"/>
+      <c r="K15" s="22"/>
+      <c r="L15" s="22"/>
+      <c r="M15" s="22"/>
+      <c r="N15" s="22"/>
+      <c r="O15" s="27"/>
     </row>
   </sheetData>
   <autoFilter ref="A4:R15" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
@@ -1334,7 +1348,7 @@
     <mergeCell ref="A2:Q2"/>
     <mergeCell ref="A3:Q3"/>
   </mergeCells>
-  <phoneticPr fontId="6" type="noConversion"/>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <extLst>
@@ -1355,253 +1369,253 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:B44"/>
-  <sheetFormatPr defaultColWidth="8.75" defaultRowHeight="16.5"/>
+  <sheetFormatPr defaultColWidth="8.75" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="47.75" style="4" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="22.5" style="4" bestFit="1" customWidth="1"/>
-    <col min="3" max="16384" width="8.75" style="4"/>
+    <col min="1" max="1" width="47.75" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="22.5" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="16384" width="8.75" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2">
-      <c r="A1" s="3" t="s">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:2">
-      <c r="A2" s="4" t="s">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2" s="2" t="s">
         <v>13</v>
       </c>
       <c r="B2" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="3" spans="1:2">
-      <c r="A3" s="4" t="s">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A3" s="2" t="s">
         <v>14</v>
       </c>
       <c r="B3" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="4" spans="1:2">
-      <c r="A4" s="4" t="s">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A4" s="2" t="s">
         <v>15</v>
       </c>
       <c r="B4" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="5" spans="1:2">
-      <c r="A5" s="4" t="s">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A5" s="2" t="s">
         <v>16</v>
       </c>
       <c r="B5" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="6" spans="1:2">
-      <c r="A6" s="4" t="s">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A6" s="2" t="s">
         <v>17</v>
       </c>
       <c r="B6" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="7" spans="1:2">
-      <c r="A7" s="4" t="s">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A7" s="2" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="8" spans="1:2">
-      <c r="A8" s="4" t="s">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A8" s="2" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="9" spans="1:2">
-      <c r="A9" s="4" t="s">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A9" s="2" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="10" spans="1:2">
-      <c r="A10" s="4" t="s">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A10" s="2" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="11" spans="1:2">
-      <c r="A11" s="4" t="s">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A11" s="2" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="12" spans="1:2">
-      <c r="A12" s="4" t="s">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A12" s="2" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="13" spans="1:2">
-      <c r="A13" s="4" t="s">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A13" s="2" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="14" spans="1:2">
-      <c r="A14" s="4" t="s">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A14" s="2" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="15" spans="1:2">
-      <c r="A15" s="4" t="s">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A15" s="2" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="16" spans="1:2">
-      <c r="A16" s="4" t="s">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A16" s="2" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="17" spans="1:1">
-      <c r="A17" s="4" t="s">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A17" s="2" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="18" spans="1:1">
-      <c r="A18" s="4" t="s">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A18" s="2" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="19" spans="1:1">
-      <c r="A19" s="4" t="s">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A19" s="2" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="20" spans="1:1">
-      <c r="A20" s="4" t="s">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A20" s="2" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="21" spans="1:1">
-      <c r="A21" s="4" t="s">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A21" s="2" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="22" spans="1:1">
-      <c r="A22" s="4" t="s">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A22" s="2" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="23" spans="1:1">
-      <c r="A23" s="4" t="s">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A23" s="2" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A24" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A25" s="2" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A26" s="2" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="24" spans="1:1">
-      <c r="A24" s="4" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="25" spans="1:1">
-      <c r="A25" s="4" t="s">
+    <row r="27" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A27" s="2" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A28" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A29" s="2" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A30" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A31" s="2" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A32" s="2" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="26" spans="1:1">
-      <c r="A26" s="4" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="27" spans="1:1">
-      <c r="A27" s="4" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="28" spans="1:1">
-      <c r="A28" s="4" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="29" spans="1:1">
-      <c r="A29" s="4" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="30" spans="1:1">
-      <c r="A30" s="4" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="31" spans="1:1">
-      <c r="A31" s="4" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="32" spans="1:1">
-      <c r="A32" s="4" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="33" spans="1:1">
-      <c r="A33" s="4" t="s">
+    <row r="33" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A33" s="2" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="34" spans="1:1">
-      <c r="A34" s="4" t="s">
+    <row r="34" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A34" s="2" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="35" spans="1:1">
-      <c r="A35" s="4" t="s">
+    <row r="35" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A35" s="2" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="36" spans="1:1">
-      <c r="A36" s="4" t="s">
+    <row r="36" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A36" s="2" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="37" spans="1:1">
-      <c r="A37" s="4" t="s">
+    <row r="37" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A37" s="2" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="38" spans="1:1">
-      <c r="A38" s="4" t="s">
+    <row r="38" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A38" s="2" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="39" spans="1:1">
-      <c r="A39" s="4" t="s">
+    <row r="39" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A39" s="2" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="40" spans="1:1">
-      <c r="A40" s="4" t="s">
+    <row r="40" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A40" s="2" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="41" spans="1:1">
-      <c r="A41" s="4" t="s">
+    <row r="41" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A41" s="2" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="42" spans="1:1">
-      <c r="A42" s="4" t="s">
+    <row r="42" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A42" s="2" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="43" spans="1:1">
-      <c r="A43" s="4" t="s">
+    <row r="43" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A43" s="2" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="44" spans="1:1">
-      <c r="A44" s="4" t="s">
+    <row r="44" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A44" s="2" t="s">
         <v>48</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="6" type="noConversion"/>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>

--- a/templates/form_template.xlsx
+++ b/templates/form_template.xlsx
@@ -245,7 +245,7 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>KR-Domestic Business Travel - Car Rental/Fuel Costs</t>
+    <t>KR-Domestic Business Travel - Car Rental</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
